--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/anova/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/anova/anova_taxa.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>467.86</v>
+        <v>232.95</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>815.5</v>
+        <v>1528.01</v>
       </c>
       <c r="F2" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G2" t="n">
-        <v>65.98</v>
+        <v>23.4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.69 ± 0.12</t>
+          <t>1.49 ± 0.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.26 ± 0.38</t>
+          <t>3.77 ± 0.41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.01 ± 0.40</t>
+          <t>1.26 ± 0.16</t>
         </is>
       </c>
     </row>
@@ -531,23 +531,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>138.68</v>
+        <v>93.69</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>794.12</v>
+        <v>837.1</v>
       </c>
       <c r="F3" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G3" t="n">
-        <v>20.08</v>
+        <v>17.18</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.96 ± 0.15</t>
+          <t>4.69 ± 0.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.15 ± 0.26</t>
+          <t>3.67 ± 0.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.43 ± 0.31</t>
+          <t>5.27 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -576,42 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>81.51000000000001</v>
+        <v>59.94</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>490.46</v>
+        <v>935.96</v>
       </c>
       <c r="F4" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G4" t="n">
-        <v>19.11</v>
+        <v>9.83</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0001***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.63 ± 0.09</t>
+          <t>2.48 ± 0.17</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.11 ± 0.30</t>
+          <t>1.13 ± 0.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.26 ± 0.33</t>
+          <t>2.21 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>88.41</v>
+        <v>15.12</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>620.01</v>
+        <v>314.38</v>
       </c>
       <c r="F5" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4</v>
+        <v>7.38</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0007***</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.03 ± 0.12</t>
+          <t>0.88 ± 0.11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.47 ± 0.33</t>
+          <t>0.20 ± 0.10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4.73 ± 0.20</t>
+          <t>0.61 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76.36</v>
+        <v>5.28</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>724</v>
+        <v>147.11</v>
       </c>
       <c r="F6" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G6" t="n">
-        <v>12.13</v>
+        <v>5.51</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0045**</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.67 ± 0.15</t>
+          <t>0.46 ± 0.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.32 ± 0.25</t>
+          <t>0.06 ± 0.04</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.99 ± 0.24</t>
+          <t>0.32 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -711,42 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.12</v>
+        <v>45.27</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>77.31</v>
+        <v>1278.41</v>
       </c>
       <c r="F7" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G7" t="n">
-        <v>7.62</v>
+        <v>5.44</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0006***</t>
+          <t>0.0048**</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.12 ± 0.03</t>
+          <t>3.40 ± 0.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.44 ± 0.14</t>
+          <t>2.23 ± 0.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.41 ± 0.14</t>
+          <t>3.15 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -756,42 +756,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.98</v>
+        <v>9.58</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>208.81</v>
+        <v>274.02</v>
       </c>
       <c r="F8" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G8" t="n">
-        <v>6.6</v>
+        <v>5.37</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0016**</t>
+          <t>0.0051**</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.46 ± 0.07</t>
+          <t>0.63 ± 0.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.13 ± 0.09</t>
+          <t>0.18 ± 0.09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.96 ± 0.26</t>
+          <t>0.30 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.9</v>
+        <v>3.34</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>253.46</v>
+        <v>117.84</v>
       </c>
       <c r="F9" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G9" t="n">
-        <v>5.85</v>
+        <v>4.35</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0033**</t>
+          <t>0.0138*</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.51 ± 0.09</t>
+          <t>0.34 ± 0.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.13 ± 0.08</t>
+          <t>0.02 ± 0.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.99 ± 0.27</t>
+          <t>0.20 ± 0.04</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.880000000000001</v>
+        <v>20.47</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>221.36</v>
+        <v>738.09</v>
       </c>
       <c r="F10" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G10" t="n">
-        <v>4.61</v>
+        <v>4.26</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0108*</t>
+          <t>0.0150*</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.46 ± 0.07</t>
+          <t>1.19 ± 0.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.49 ± 0.16</t>
+          <t>1.83 ± 0.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.06 ± 0.26</t>
+          <t>1.07 ± 0.12</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.62</v>
+        <v>5.75</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>139.42</v>
+        <v>415.51</v>
       </c>
       <c r="F11" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G11" t="n">
-        <v>3.81</v>
+        <v>2.13</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0235*</t>
+          <t>0.1211</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.48 ± 0.07</t>
+          <t>0.77 ± 0.11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.14 ± 0.07</t>
+          <t>0.37 ± 0.12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.52 ± 0.13</t>
+          <t>0.75 ± 0.10</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>111.62</v>
+        <v>269.3</v>
       </c>
       <c r="F12" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G12" t="n">
-        <v>2.85</v>
+        <v>1.74</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0599.</t>
+          <t>0.1773</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.31 ± 0.06</t>
+          <t>0.48 ± 0.10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.03 ± 0.03</t>
+          <t>0.58 ± 0.15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.26 ± 0.11</t>
+          <t>0.32 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -981,42 +981,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.13</v>
+        <v>2.63</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>174.56</v>
+        <v>244.03</v>
       </c>
       <c r="F13" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>1.65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0679.</t>
+          <t>0.1929</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.33 ± 0.07</t>
+          <t>0.31 ± 0.08</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.27 ± 0.12</t>
+          <t>0.53 ± 0.17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.72 ± 0.20</t>
+          <t>0.49 ± 0.07</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.77</v>
+        <v>0.35</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>139.1</v>
+        <v>120.36</v>
       </c>
       <c r="F14" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G14" t="n">
-        <v>2.29</v>
+        <v>0.44</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.1033</t>
+          <t>0.6425</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.19 ± 0.06</t>
+          <t>0.21 ± 0.06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.46 ± 0.15</t>
+          <t>0.12 ± 0.07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.25 ± 0.14</t>
+          <t>0.21 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>218.98</v>
+        <v>159.64</v>
       </c>
       <c r="F15" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G15" t="n">
-        <v>1.89</v>
+        <v>0.38</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.1537</t>
+          <t>0.6834</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.37 ± 0.08</t>
+          <t>0.43 ± 0.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.64 ± 0.15</t>
+          <t>0.32 ± 0.12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.24 ± 0.13</t>
+          <t>0.37 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.57</v>
+        <v>0.22</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>110.01</v>
+        <v>415.66</v>
       </c>
       <c r="F16" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G16" t="n">
-        <v>1.64</v>
+        <v>0.08</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.9227</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.24 ± 0.06</t>
+          <t>0.45 ± 0.10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.04 ± 0.03</t>
+          <t>0.47 ± 0.17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.26 ± 0.10</t>
+          <t>0.51 ± 0.10</t>
         </is>
       </c>
     </row>
@@ -1165,28 +1165,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.73</v>
+        <v>0.01</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>109.88</v>
+        <v>115.55</v>
       </c>
       <c r="F17" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="G17" t="n">
-        <v>0.77</v>
+        <v>0.02</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.4659</t>
+          <t>0.9807</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.21 ± 0.05</t>
+          <t>0.20 ± 0.05</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.37 ± 0.15</t>
+          <t>0.19 ± 0.05</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="J19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K19" t="n">
-        <v>28</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20">

--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/anova/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/anova/anova_taxa.xlsx
@@ -486,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>232.95</v>
+        <v>309.16</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1528.01</v>
+        <v>1014.52</v>
       </c>
       <c r="F2" t="n">
         <v>307</v>
       </c>
       <c r="G2" t="n">
-        <v>23.4</v>
+        <v>46.78</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.49 ± 0.22</t>
+          <t>3.86 ± 0.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.77 ± 0.41</t>
+          <t>2.64 ± 0.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.26 ± 0.16</t>
+          <t>1.65 ± 0.16</t>
         </is>
       </c>
     </row>
@@ -531,23 +531,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93.69</v>
+        <v>122.13</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>837.1</v>
+        <v>873.77</v>
       </c>
       <c r="F3" t="n">
         <v>307</v>
       </c>
       <c r="G3" t="n">
-        <v>17.18</v>
+        <v>21.45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.69 ± 0.16</t>
+          <t>2.58 ± 0.13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.67 ± 0.34</t>
+          <t>2.33 ± 0.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.27 ± 0.11</t>
+          <t>1.18 ± 0.15</t>
         </is>
       </c>
     </row>
@@ -576,42 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Dreissena</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>59.94</v>
+        <v>172.31</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>935.96</v>
+        <v>1588.65</v>
       </c>
       <c r="F4" t="n">
         <v>307</v>
       </c>
       <c r="G4" t="n">
-        <v>9.83</v>
+        <v>16.65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0001***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.48 ± 0.17</t>
+          <t>1.13 ± 0.15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.13 ± 0.22</t>
+          <t>2.95 ± 0.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.21 ± 0.14</t>
+          <t>2.55 ± 0.27</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.12</v>
+        <v>34.98</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>314.38</v>
+        <v>380.9</v>
       </c>
       <c r="F5" t="n">
         <v>307</v>
       </c>
       <c r="G5" t="n">
-        <v>7.38</v>
+        <v>14.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0007***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.88 ± 0.11</t>
+          <t>0.24 ± 0.05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.20 ± 0.10</t>
+          <t>0.43 ± 0.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.61 ± 0.08</t>
+          <t>0.99 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.28</v>
+        <v>12.33</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>147.11</v>
+        <v>147.71</v>
       </c>
       <c r="F6" t="n">
         <v>307</v>
       </c>
       <c r="G6" t="n">
-        <v>5.51</v>
+        <v>12.81</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0045**</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.46 ± 0.07</t>
+          <t>0.23 ± 0.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.06 ± 0.04</t>
+          <t>0.48 ± 0.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.32 ± 0.06</t>
+          <t>0.67 ± 0.10</t>
         </is>
       </c>
     </row>
@@ -711,42 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45.27</v>
+        <v>48.27</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1278.41</v>
+        <v>710.3</v>
       </c>
       <c r="F7" t="n">
         <v>307</v>
       </c>
       <c r="G7" t="n">
-        <v>5.44</v>
+        <v>10.43</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0048**</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.40 ± 0.19</t>
+          <t>0.94 ± 0.10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.23 ± 0.30</t>
+          <t>1.24 ± 0.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3.15 ± 0.17</t>
+          <t>1.82 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -756,42 +756,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.58</v>
+        <v>11.95</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>274.02</v>
+        <v>234.71</v>
       </c>
       <c r="F8" t="n">
         <v>307</v>
       </c>
       <c r="G8" t="n">
-        <v>5.37</v>
+        <v>7.82</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0051**</t>
+          <t>0.0005***</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.63 ± 0.12</t>
+          <t>0.53 ± 0.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.18 ± 0.09</t>
+          <t>0.70 ± 0.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.30 ± 0.06</t>
+          <t>0.13 ± 0.05</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.34</v>
+        <v>5.67</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>117.84</v>
+        <v>115.04</v>
       </c>
       <c r="F9" t="n">
         <v>307</v>
       </c>
       <c r="G9" t="n">
-        <v>4.35</v>
+        <v>7.56</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0138*</t>
+          <t>0.0006***</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.34 ± 0.08</t>
+          <t>0.30 ± 0.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.02 ± 0.01</t>
+          <t>0.07 ± 0.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.20 ± 0.04</t>
+          <t>0.01 ± 0.01</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.47</v>
+        <v>11.58</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>738.09</v>
+        <v>260.78</v>
       </c>
       <c r="F10" t="n">
         <v>307</v>
       </c>
       <c r="G10" t="n">
-        <v>4.26</v>
+        <v>6.81</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0150*</t>
+          <t>0.0013**</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.19 ± 0.14</t>
+          <t>0.31 ± 0.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.83 ± 0.28</t>
+          <t>0.16 ± 0.09</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.07 ± 0.12</t>
+          <t>0.71 ± 0.13</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>415.51</v>
+        <v>146.56</v>
       </c>
       <c r="F11" t="n">
         <v>307</v>
       </c>
       <c r="G11" t="n">
-        <v>2.13</v>
+        <v>6.11</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.0025**</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.77 ± 0.11</t>
+          <t>0.44 ± 0.05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.37 ± 0.12</t>
+          <t>0.15 ± 0.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.75 ± 0.10</t>
+          <t>0.16 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.05</v>
+        <v>10.71</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>269.3</v>
+        <v>272.9</v>
       </c>
       <c r="F12" t="n">
         <v>307</v>
       </c>
       <c r="G12" t="n">
-        <v>1.74</v>
+        <v>6.02</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.1773</t>
+          <t>0.0027**</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.48 ± 0.10</t>
+          <t>0.54 ± 0.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.58 ± 0.15</t>
+          <t>0.05 ± 0.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.32 ± 0.06</t>
+          <t>0.20 ± 0.07</t>
         </is>
       </c>
     </row>
@@ -981,42 +981,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.63</v>
+        <v>15.6</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>244.03</v>
+        <v>405.67</v>
       </c>
       <c r="F13" t="n">
         <v>307</v>
       </c>
       <c r="G13" t="n">
-        <v>1.65</v>
+        <v>5.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.1929</t>
+          <t>0.0031**</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.31 ± 0.08</t>
+          <t>0.52 ± 0.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.53 ± 0.17</t>
+          <t>0.91 ± 0.26</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.49 ± 0.07</t>
+          <t>1.00 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.35</v>
+        <v>8.06</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>120.36</v>
+        <v>321.44</v>
       </c>
       <c r="F14" t="n">
         <v>307</v>
       </c>
       <c r="G14" t="n">
-        <v>0.44</v>
+        <v>3.85</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.6425</t>
+          <t>0.0223*</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.21 ± 0.06</t>
+          <t>0.58 ± 0.08</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.12 ± 0.07</t>
+          <t>0.36 ± 0.13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.21 ± 0.06</t>
+          <t>0.87 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4</v>
+        <v>1.43</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>159.64</v>
+        <v>114.14</v>
       </c>
       <c r="F15" t="n">
         <v>307</v>
       </c>
       <c r="G15" t="n">
-        <v>0.38</v>
+        <v>1.93</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.6834</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.43 ± 0.07</t>
+          <t>0.22 ± 0.05</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.32 ± 0.12</t>
+          <t>0.31 ± 0.17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.37 ± 0.06</t>
+          <t>0.09 ± 0.04</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>415.66</v>
+        <v>119.73</v>
       </c>
       <c r="F16" t="n">
         <v>307</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.9227</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.45 ± 0.10</t>
+          <t>0.19 ± 0.04</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.47 ± 0.17</t>
+          <t>0.09 ± 0.05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.51 ± 0.10</t>
+          <t>0.32 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01</v>
+        <v>6.01</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>115.55</v>
+        <v>924.79</v>
       </c>
       <c r="F17" t="n">
         <v>307</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.9807</t>
+          <t>0.3702</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.20 ± 0.05</t>
+          <t>4.89 ± 0.12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.18 ± 0.12</t>
+          <t>4.40 ± 0.39</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.19 ± 0.05</t>
+          <t>4.83 ± 0.20</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="J19" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>156</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20">

--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/anova/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/anova/anova_taxa.xlsx
@@ -486,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>309.16</v>
+        <v>125.21</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1014.52</v>
+        <v>870.6900000000001</v>
       </c>
       <c r="F2" t="n">
         <v>307</v>
       </c>
       <c r="G2" t="n">
-        <v>46.78</v>
+        <v>22.07</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.86 ± 0.14</t>
+          <t>2.36 ± 0.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.64 ± 0.37</t>
+          <t>3.55 ± 0.33</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.65 ± 0.16</t>
+          <t>0.87 ± 0.16</t>
         </is>
       </c>
     </row>
@@ -531,23 +531,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>122.13</v>
+        <v>52.25</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>873.77</v>
+        <v>363.62</v>
       </c>
       <c r="F3" t="n">
         <v>307</v>
       </c>
       <c r="G3" t="n">
-        <v>21.45</v>
+        <v>22.06</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.58 ± 0.13</t>
+          <t>0.27 ± 0.05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.33 ± 0.35</t>
+          <t>0.76 ± 0.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.18 ± 0.15</t>
+          <t>1.34 ± 0.26</t>
         </is>
       </c>
     </row>
@@ -576,23 +576,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>172.31</v>
+        <v>18.56</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1588.65</v>
+        <v>141.48</v>
       </c>
       <c r="F4" t="n">
         <v>307</v>
       </c>
       <c r="G4" t="n">
-        <v>16.65</v>
+        <v>20.13</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -601,17 +601,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.13 ± 0.15</t>
+          <t>0.26 ± 0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.95 ± 0.54</t>
+          <t>1.09 ± 0.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.55 ± 0.27</t>
+          <t>0.78 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -621,23 +621,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34.98</v>
+        <v>127.44</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>380.9</v>
+        <v>1196.24</v>
       </c>
       <c r="F5" t="n">
         <v>307</v>
       </c>
       <c r="G5" t="n">
-        <v>14.1</v>
+        <v>16.35</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -646,17 +646,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.24 ± 0.05</t>
+          <t>3.38 ± 0.13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.43 ± 0.21</t>
+          <t>3.84 ± 0.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.99 ± 0.17</t>
+          <t>1.74 ± 0.22</t>
         </is>
       </c>
     </row>
@@ -666,23 +666,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Dreissena</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12.33</v>
+        <v>165.42</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>147.71</v>
+        <v>1595.54</v>
       </c>
       <c r="F6" t="n">
         <v>307</v>
       </c>
       <c r="G6" t="n">
-        <v>12.81</v>
+        <v>15.91</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -691,17 +691,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.23 ± 0.03</t>
+          <t>1.33 ± 0.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.48 ± 0.17</t>
+          <t>3.42 ± 0.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.67 ± 0.10</t>
+          <t>3.02 ± 0.33</t>
         </is>
       </c>
     </row>
@@ -711,23 +711,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.27</v>
+        <v>22.16</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>710.3</v>
+        <v>250.2</v>
       </c>
       <c r="F7" t="n">
         <v>307</v>
       </c>
       <c r="G7" t="n">
-        <v>10.43</v>
+        <v>13.59</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -736,17 +736,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.94 ± 0.10</t>
+          <t>0.31 ± 0.05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.24 ± 0.33</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.82 ± 0.17</t>
+          <t>0.98 ± 0.20</t>
         </is>
       </c>
     </row>
@@ -756,42 +756,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.95</v>
+        <v>48.67</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>234.71</v>
+        <v>709.89</v>
       </c>
       <c r="F8" t="n">
         <v>307</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82</v>
+        <v>10.52</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0005***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.53 ± 0.07</t>
+          <t>1.02 ± 0.10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.70 ± 0.21</t>
+          <t>1.84 ± 0.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.13 ± 0.05</t>
+          <t>2.01 ± 0.20</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.67</v>
+        <v>15.42</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>115.04</v>
+        <v>231.24</v>
       </c>
       <c r="F9" t="n">
         <v>307</v>
       </c>
       <c r="G9" t="n">
-        <v>7.56</v>
+        <v>10.24</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0006***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.30 ± 0.06</t>
+          <t>0.48 ± 0.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.07 ± 0.07</t>
+          <t>1.17 ± 0.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.01 ± 0.01</t>
+          <t>0.04 ± 0.02</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.58</v>
+        <v>6.7</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>260.78</v>
+        <v>114.48</v>
       </c>
       <c r="F10" t="n">
         <v>307</v>
       </c>
       <c r="G10" t="n">
-        <v>6.81</v>
+        <v>8.98</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0013**</t>
+          <t>0.0002***</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.31 ± 0.06</t>
+          <t>0.14 ± 0.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.16 ± 0.09</t>
+          <t>0.35 ± 0.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.71 ± 0.13</t>
+          <t>0.52 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.83</v>
+        <v>13.42</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>146.56</v>
+        <v>407.85</v>
       </c>
       <c r="F11" t="n">
         <v>307</v>
       </c>
       <c r="G11" t="n">
-        <v>6.11</v>
+        <v>5.05</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0025**</t>
+          <t>0.0069**</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.44 ± 0.05</t>
+          <t>0.59 ± 0.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.15 ± 0.07</t>
+          <t>1.03 ± 0.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.16 ± 0.06</t>
+          <t>1.11 ± 0.18</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.71</v>
+        <v>8.24</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>272.9</v>
+        <v>321.26</v>
       </c>
       <c r="F12" t="n">
         <v>307</v>
       </c>
       <c r="G12" t="n">
-        <v>6.02</v>
+        <v>3.94</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0027**</t>
+          <t>0.0205*</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.54 ± 0.08</t>
+          <t>0.56 ± 0.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.05 ± 0.04</t>
+          <t>1.12 ± 0.32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.20 ± 0.07</t>
+          <t>0.91 ± 0.13</t>
         </is>
       </c>
     </row>
@@ -981,42 +981,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.6</v>
+        <v>2.95</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>405.67</v>
+        <v>149.43</v>
       </c>
       <c r="F13" t="n">
         <v>307</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>3.04</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0031**</t>
+          <t>0.0495*</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.52 ± 0.07</t>
+          <t>0.37 ± 0.05</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.91 ± 0.26</t>
+          <t>0.52 ± 0.24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.00 ± 0.14</t>
+          <t>0.13 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.06</v>
+        <v>2.32</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>321.44</v>
+        <v>118.39</v>
       </c>
       <c r="F14" t="n">
         <v>307</v>
       </c>
       <c r="G14" t="n">
-        <v>3.85</v>
+        <v>3.01</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0223*</t>
+          <t>0.0509.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.58 ± 0.08</t>
+          <t>0.24 ± 0.04</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.36 ± 0.13</t>
+          <t>0.16 ± 0.16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.87 ± 0.11</t>
+          <t>0.01 ± 0.01</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.43</v>
+        <v>12.02</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>114.14</v>
+        <v>918.78</v>
       </c>
       <c r="F15" t="n">
         <v>307</v>
       </c>
       <c r="G15" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.22 ± 0.05</t>
+          <t>4.92 ± 0.11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.31 ± 0.17</t>
+          <t>4.07 ± 0.42</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.09 ± 0.04</t>
+          <t>4.59 ± 0.24</t>
         </is>
       </c>
     </row>
@@ -1116,27 +1116,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>119.73</v>
+        <v>114.42</v>
       </c>
       <c r="F16" t="n">
         <v>307</v>
       </c>
       <c r="G16" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.2152</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.09 ± 0.05</t>
+          <t>0.46 ± 0.27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.32 ± 0.08</t>
+          <t>0.12 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.01</v>
+        <v>1.01</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>924.79</v>
+        <v>282.59</v>
       </c>
       <c r="F17" t="n">
         <v>307</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.3702</t>
+          <t>0.5786</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.89 ± 0.12</t>
+          <t>0.42 ± 0.06</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4.40 ± 0.39</t>
+          <t>0.28 ± 0.18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4.83 ± 0.20</t>
+          <t>0.29 ± 0.12</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="J19" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">

--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/anova/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/anova/anova_taxa.xlsx
@@ -486,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125.21</v>
+        <v>255.52</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>870.6900000000001</v>
+        <v>1068.15</v>
       </c>
       <c r="F2" t="n">
         <v>307</v>
       </c>
       <c r="G2" t="n">
-        <v>22.07</v>
+        <v>36.72</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.36 ± 0.12</t>
+          <t>3.67 ± 0.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.55 ± 0.33</t>
+          <t>2.82 ± 0.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.87 ± 0.16</t>
+          <t>1.61 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -531,23 +531,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>52.25</v>
+        <v>139.63</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>363.62</v>
+        <v>856.26</v>
       </c>
       <c r="F3" t="n">
         <v>307</v>
       </c>
       <c r="G3" t="n">
-        <v>22.06</v>
+        <v>25.03</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.27 ± 0.05</t>
+          <t>2.46 ± 0.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.76 ± 0.43</t>
+          <t>4.12 ± 0.47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.34 ± 0.26</t>
+          <t>1.11 ± 0.15</t>
         </is>
       </c>
     </row>
@@ -580,19 +580,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.56</v>
+        <v>20.18</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>141.48</v>
+        <v>139.86</v>
       </c>
       <c r="F4" t="n">
         <v>307</v>
       </c>
       <c r="G4" t="n">
-        <v>20.13</v>
+        <v>22.15</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -601,17 +601,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.26 ± 0.03</t>
+          <t>0.22 ± 0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.09 ± 0.37</t>
+          <t>0.86 ± 0.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.78 ± 0.14</t>
+          <t>0.77 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -621,23 +621,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>127.44</v>
+        <v>41.78</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1196.24</v>
+        <v>374.1</v>
       </c>
       <c r="F5" t="n">
         <v>307</v>
       </c>
       <c r="G5" t="n">
-        <v>16.35</v>
+        <v>17.14</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -646,17 +646,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.38 ± 0.13</t>
+          <t>0.25 ± 0.05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.84 ± 0.51</t>
+          <t>1.13 ± 0.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.74 ± 0.22</t>
+          <t>1.05 ± 0.19</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>165.42</v>
+        <v>134.76</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1595.54</v>
+        <v>1626.2</v>
       </c>
       <c r="F6" t="n">
         <v>307</v>
       </c>
       <c r="G6" t="n">
-        <v>15.91</v>
+        <v>12.72</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -691,17 +691,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.33 ± 0.14</t>
+          <t>1.32 ± 0.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.42 ± 0.61</t>
+          <t>4.24 ± 0.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.02 ± 0.33</t>
+          <t>2.50 ± 0.28</t>
         </is>
       </c>
     </row>
@@ -711,42 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.16</v>
+        <v>47.1</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>250.2</v>
+        <v>711.46</v>
       </c>
       <c r="F7" t="n">
         <v>307</v>
       </c>
       <c r="G7" t="n">
-        <v>13.59</v>
+        <v>10.16</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0001***</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.31 ± 0.05</t>
+          <t>1.03 ± 0.10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.31 ± 0.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.98 ± 0.20</t>
+          <t>1.85 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -756,42 +756,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48.67</v>
+        <v>14.73</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>709.89</v>
+        <v>231.94</v>
       </c>
       <c r="F8" t="n">
         <v>307</v>
       </c>
       <c r="G8" t="n">
-        <v>10.52</v>
+        <v>9.75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0001***</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.02 ± 0.10</t>
+          <t>0.56 ± 0.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.84 ± 0.53</t>
+          <t>0.61 ± 0.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.01 ± 0.20</t>
+          <t>0.07 ± 0.03</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.42</v>
+        <v>24.61</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>231.24</v>
+        <v>396.66</v>
       </c>
       <c r="F9" t="n">
         <v>307</v>
       </c>
       <c r="G9" t="n">
-        <v>10.24</v>
+        <v>9.52</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0001***</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.48 ± 0.06</t>
+          <t>0.52 ± 0.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.17 ± 0.45</t>
+          <t>1.10 ± 0.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.04 ± 0.02</t>
+          <t>1.14 ± 0.15</t>
         </is>
       </c>
     </row>
@@ -846,23 +846,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.7</v>
+        <v>14.42</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>114.48</v>
+        <v>257.94</v>
       </c>
       <c r="F10" t="n">
         <v>307</v>
       </c>
       <c r="G10" t="n">
-        <v>8.98</v>
+        <v>8.58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -871,17 +871,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.14 ± 0.03</t>
+          <t>0.30 ± 0.05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.35 ± 0.21</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.52 ± 0.14</t>
+          <t>0.77 ± 0.15</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13.42</v>
+        <v>3.65</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>407.85</v>
+        <v>117.05</v>
       </c>
       <c r="F11" t="n">
         <v>307</v>
       </c>
       <c r="G11" t="n">
-        <v>5.05</v>
+        <v>4.79</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0069**</t>
+          <t>0.0089**</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.59 ± 0.07</t>
+          <t>0.26 ± 0.05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.03 ± 0.31</t>
+          <t>0.24 ± 0.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.11 ± 0.18</t>
+          <t>0.02 ± 0.01</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.24</v>
+        <v>4.59</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>321.26</v>
+        <v>147.79</v>
       </c>
       <c r="F12" t="n">
         <v>307</v>
       </c>
       <c r="G12" t="n">
-        <v>3.94</v>
+        <v>4.77</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0205*</t>
+          <t>0.0091**</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.56 ± 0.07</t>
+          <t>0.41 ± 0.05</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.12 ± 0.32</t>
+          <t>0.21 ± 0.12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.91 ± 0.13</t>
+          <t>0.13 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -981,42 +981,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.95</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>149.43</v>
+        <v>320.05</v>
       </c>
       <c r="F13" t="n">
         <v>307</v>
       </c>
       <c r="G13" t="n">
-        <v>3.04</v>
+        <v>4.53</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0495*</t>
+          <t>0.0115*</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.37 ± 0.05</t>
+          <t>0.53 ± 0.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.52 ± 0.24</t>
+          <t>0.82 ± 0.36</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.13 ± 0.06</t>
+          <t>0.92 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>118.39</v>
+        <v>113.38</v>
       </c>
       <c r="F14" t="n">
         <v>307</v>
       </c>
       <c r="G14" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0509.</t>
+          <t>0.0529.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.24 ± 0.04</t>
+          <t>0.21 ± 0.04</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.16 ± 0.16</t>
+          <t>0.60 ± 0.36</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.01 ± 0.01</t>
+          <t>0.09 ± 0.04</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12.02</v>
+        <v>1.88</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>918.78</v>
+        <v>119.29</v>
       </c>
       <c r="F15" t="n">
         <v>307</v>
       </c>
       <c r="G15" t="n">
-        <v>2.01</v>
+        <v>2.42</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.0902.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.92 ± 0.11</t>
+          <t>0.17 ± 0.04</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.07 ± 0.42</t>
+          <t>0.13 ± 0.13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.59 ± 0.24</t>
+          <t>0.35 ± 0.09</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.15</v>
+        <v>3.94</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>114.42</v>
+        <v>279.66</v>
       </c>
       <c r="F16" t="n">
         <v>307</v>
       </c>
       <c r="G16" t="n">
-        <v>1.54</v>
+        <v>2.16</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.2152</t>
+          <t>0.1168</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.19 ± 0.04</t>
+          <t>0.47 ± 0.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.46 ± 0.27</t>
+          <t>0.16 ± 0.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.12 ± 0.06</t>
+          <t>0.22 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>282.59</v>
+        <v>928.1</v>
       </c>
       <c r="F17" t="n">
         <v>307</v>
       </c>
       <c r="G17" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.5786</t>
+          <t>0.6402</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.42 ± 0.06</t>
+          <t>4.81 ± 0.12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.28 ± 0.18</t>
+          <t>4.34 ± 0.64</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.29 ± 0.12</t>
+          <t>4.92 ± 0.19</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
